--- a/data/descargas/venta_total.xlsx
+++ b/data/descargas/venta_total.xlsx
@@ -685,7 +685,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reporte generado: 01-01-2026 07:13 a. m. </t>
+          <t xml:space="preserve">Reporte generado: 01-01-2026 07:37 a. m. </t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>

--- a/data/descargas/venta_total.xlsx
+++ b/data/descargas/venta_total.xlsx
@@ -685,7 +685,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reporte generado: 01-01-2026 07:37 a. m. </t>
+          <t>Reporte generado: 01-01-2026 03:24 p. m.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>

--- a/data/descargas/venta_total.xlsx
+++ b/data/descargas/venta_total.xlsx
@@ -685,7 +685,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reporte generado: 01-02-2026 07:52 a. m. </t>
+          <t>Reporte generado: 01-02-2026 03:27 p. m.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>

--- a/data/descargas/venta_total.xlsx
+++ b/data/descargas/venta_total.xlsx
@@ -685,7 +685,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reporte generado: 01-03-2026 07:22 a. m. </t>
+          <t xml:space="preserve">Reporte generado: 01-03-2026 07:49 a. m. </t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>

--- a/data/descargas/venta_total.xlsx
+++ b/data/descargas/venta_total.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y4"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,66 +683,280 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reporte generado: 01-03-2026 07:49 a. m. </t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>01-03-26</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>26210522759710004180</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>LPAZ260005679</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>MEMBRESIA</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>PROMO ENERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>499</v>
+      </c>
+      <c r="J3" t="n">
+        <v>430.17</v>
+      </c>
+      <c r="K3" t="n">
+        <v>68.83</v>
+      </c>
+      <c r="L3" t="n">
+        <v>16</v>
+      </c>
+      <c r="M3" t="n">
+        <v>499</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>RECURRENTE LINEA</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Juan Jesus Palafox Encinas</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>02:02</t>
+        </is>
+      </c>
       <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Redes Sociales</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>17264</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>ARIANA SCARLETT  ROSENDO VILLALOBOS</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Renovación</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>01-03-26</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>IXTAPALUCA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>26220522759720005268</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>IXTA260006536</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>MEMBRESIA</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>PROMO ENERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>499</v>
+      </c>
+      <c r="J4" t="n">
+        <v>430.17</v>
+      </c>
+      <c r="K4" t="n">
+        <v>68.83</v>
+      </c>
+      <c r="L4" t="n">
+        <v>16</v>
+      </c>
+      <c r="M4" t="n">
+        <v>499</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>RECURRENTE LINEA</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>ACTIVO</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Jose Luis  Gonzalez Robledo</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>06:43</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Cerca de Domicilio/Trabajo</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Julio Cesar Javier Diaz </t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>16171</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>CLAUDIA DANIELA JIMENEZ SANCHEZ</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Renovación</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Reporte generado: 01-03-2026 03:26 p. m.</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>DEL 03/01/2026 A 03/01/2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
